--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Input.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="258">
   <si>
     <t>Property</t>
   </si>
@@ -486,6 +486,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -612,6 +622,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -625,24 +638,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1153,7 +1173,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="33.30859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2447,24 +2467,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2490,13 +2510,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2522,13 +2542,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2546,7 +2566,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2555,24 +2575,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2598,13 +2618,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2654,7 +2674,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2677,10 +2697,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2703,16 +2723,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2738,13 +2758,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -2762,7 +2782,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2785,10 +2805,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2811,13 +2831,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2856,7 +2876,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2866,7 +2886,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2875,24 +2895,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2995,10 +3015,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3068,16 +3088,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3103,14 +3123,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3132,16 +3152,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3190,7 +3210,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3208,15 +3228,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3242,12 +3262,14 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3296,7 +3318,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3319,10 +3341,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3345,13 +3367,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3402,7 +3424,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3411,7 +3433,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3420,15 +3442,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3451,16 +3473,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3510,7 +3532,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3519,7 +3541,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3528,15 +3550,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3562,13 +3584,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3618,7 +3640,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3630,7 +3652,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3641,13 +3663,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3669,13 +3691,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3726,7 +3748,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3735,24 +3757,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3855,10 +3877,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3928,16 +3950,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3963,14 +3985,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3992,16 +4014,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4050,7 +4072,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4068,15 +4090,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4102,12 +4124,14 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4117,7 +4141,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4156,7 +4180,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4179,10 +4203,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4205,13 +4229,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4262,7 +4286,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4271,7 +4295,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4280,15 +4304,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4311,16 +4335,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4370,7 +4394,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4379,7 +4403,7 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>75</v>
@@ -4388,15 +4412,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4422,13 +4446,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4466,7 +4490,7 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4476,7 +4500,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4488,7 +4512,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4499,10 +4523,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4605,10 +4629,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4678,16 +4702,16 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>111</v>
@@ -4713,14 +4737,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4742,16 +4766,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4800,7 +4824,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4818,15 +4842,15 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4852,12 +4876,14 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4906,7 +4932,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4929,10 +4955,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4955,13 +4981,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5012,7 +5038,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5021,7 +5047,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -5030,15 +5056,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5061,16 +5087,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5120,7 +5146,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5129,7 +5155,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5138,15 +5164,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5172,13 +5198,13 @@
         <v>75</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5228,7 +5254,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5240,7 +5266,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5251,13 +5277,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5279,16 +5305,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5338,7 +5364,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5350,7 +5376,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5361,10 +5387,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5467,10 +5493,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5540,16 +5566,16 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>111</v>
@@ -5575,14 +5601,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5604,16 +5630,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5662,7 +5688,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5680,15 +5706,15 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5714,12 +5740,14 @@
         <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5729,7 +5757,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5768,7 +5796,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5791,10 +5819,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5817,13 +5845,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5874,7 +5902,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5883,7 +5911,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5892,15 +5920,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5923,16 +5951,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5982,7 +6010,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -5991,7 +6019,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -6000,15 +6028,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6034,13 +6062,13 @@
         <v>75</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6090,7 +6118,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6102,7 +6130,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6113,13 +6141,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6141,16 +6169,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6200,7 +6228,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6212,7 +6240,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6223,10 +6251,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6329,10 +6357,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6402,16 +6430,16 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>111</v>
@@ -6437,14 +6465,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6466,16 +6494,16 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6524,7 +6552,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6542,15 +6570,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6576,12 +6604,14 @@
         <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6591,7 +6621,7 @@
         <v>75</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>75</v>
@@ -6630,7 +6660,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6653,10 +6683,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6679,13 +6709,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6736,7 +6766,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6745,7 +6775,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6754,15 +6784,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6785,16 +6815,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6844,7 +6874,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6862,15 +6892,15 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6896,13 +6926,13 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6952,7 +6982,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6964,7 +6994,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Input.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Close-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -486,16 +486,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -622,9 +612,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -638,8 +625,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -656,13 +643,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1173,7 +1153,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="33.30859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2467,24 +2447,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2510,13 +2490,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2542,31 +2522,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2575,24 +2555,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2618,13 +2598,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2674,7 +2654,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2697,10 +2677,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2723,16 +2703,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2758,31 +2738,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2805,10 +2785,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2831,13 +2811,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2876,7 +2856,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2886,7 +2866,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2895,24 +2875,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3015,10 +2995,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3088,16 +3068,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3123,14 +3103,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3152,16 +3132,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3210,7 +3190,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3228,15 +3208,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3262,14 +3242,12 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3318,7 +3296,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3341,10 +3319,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3367,13 +3345,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3424,16 +3402,16 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3442,15 +3420,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3473,16 +3451,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3532,7 +3510,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3541,7 +3519,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3550,15 +3528,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3584,13 +3562,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3640,7 +3618,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3652,7 +3630,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3663,13 +3641,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3691,13 +3669,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3748,7 +3726,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3757,24 +3735,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3877,10 +3855,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3950,16 +3928,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3985,14 +3963,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4014,16 +3992,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4072,7 +4050,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4090,15 +4068,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4124,14 +4102,12 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4141,7 +4117,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4180,7 +4156,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4203,10 +4179,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4229,13 +4205,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4286,16 +4262,16 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4304,15 +4280,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4335,16 +4311,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4394,7 +4370,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4403,7 +4379,7 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>75</v>
@@ -4412,15 +4388,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4446,13 +4422,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4490,7 +4466,7 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4500,7 +4476,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4512,7 +4488,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4523,10 +4499,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4629,10 +4605,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4702,16 +4678,16 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>111</v>
@@ -4737,14 +4713,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4766,16 +4742,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4824,7 +4800,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4842,15 +4818,15 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4876,14 +4852,12 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4932,7 +4906,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4955,10 +4929,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4981,13 +4955,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5038,16 +5012,16 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI36" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -5056,15 +5030,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5087,16 +5061,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5146,7 +5120,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5155,7 +5129,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5164,15 +5138,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5198,13 +5172,13 @@
         <v>75</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5254,7 +5228,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5266,7 +5240,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5277,13 +5251,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5305,16 +5279,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5364,7 +5338,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5376,7 +5350,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5387,10 +5361,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5493,10 +5467,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5566,16 +5540,16 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>111</v>
@@ -5601,14 +5575,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5630,16 +5604,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5688,7 +5662,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5706,15 +5680,15 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5740,14 +5714,12 @@
         <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5757,7 +5729,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5796,7 +5768,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5819,10 +5791,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5845,13 +5817,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5902,16 +5874,16 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5920,15 +5892,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5951,16 +5923,16 @@
         <v>85</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6010,7 +5982,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6019,7 +5991,7 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>75</v>
@@ -6028,15 +6000,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6062,13 +6034,13 @@
         <v>75</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6118,7 +6090,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6130,7 +6102,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6141,13 +6113,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6169,16 +6141,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6228,7 +6200,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6240,7 +6212,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6251,10 +6223,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6357,10 +6329,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6430,16 +6402,16 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>111</v>
@@ -6465,14 +6437,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6494,16 +6466,16 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6552,7 +6524,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6570,15 +6542,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6604,14 +6576,12 @@
         <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6621,7 +6591,7 @@
         <v>75</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>75</v>
@@ -6660,7 +6630,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6683,10 +6653,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6709,13 +6679,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6766,16 +6736,16 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6784,15 +6754,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6815,16 +6785,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6874,7 +6844,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6892,15 +6862,15 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6926,13 +6896,13 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6982,7 +6952,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6994,7 +6964,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
